--- a/output/pdf_financials_xlsx/ENW.xlsx
+++ b/output/pdf_financials_xlsx/ENW.xlsx
@@ -5559,43 +5559,43 @@
         <v>0</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>0.101695</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>0.327</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>0.511</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>0.495</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>0.548</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>0.694</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>0.775</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0</v>
+        <v>0.515</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0</v>
+        <v>0.524</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0</v>
+        <v>0.542</v>
       </c>
     </row>
     <row r="92">
@@ -10324,7 +10324,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -13930,7 +13934,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ENW.xlsx
+++ b/output/pdf_financials_xlsx/ENW.xlsx
@@ -2049,7 +2049,7 @@
         <v>0.755132</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1.353445</v>
+        <v>-0.97129</v>
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>-4.217703</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-5.575343</v>
+        <v>-7.900078</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>-2680.697996644125</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-1145.062363550851</v>
+        <v>-1622.515778296704</v>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
@@ -52864,7 +52864,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">

--- a/output/pdf_financials_xlsx/ENW.xlsx
+++ b/output/pdf_financials_xlsx/ENW.xlsx
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.755132</v>
+        <v>0.629922</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>-0.97129</v>
+        <v>1.147256</v>
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
@@ -2057,34 +2057,34 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1.751</v>
+        <v>1.419</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>2.232</v>
+        <v>1.42</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>2.316</v>
+        <v>1.222</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1.964</v>
+        <v>0.888</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1.978</v>
+        <v>0.573</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>2.022</v>
+        <v>0.391</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>2.038</v>
+        <v>0.248</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>2.513</v>
+        <v>0.218</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>1.098</v>
+        <v>0.118</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>1.117</v>
+        <v>0.01</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>1.16</v>
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.217703</v>
+        <v>-4.342913</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-7.900078</v>
+        <v>-5.781532</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -2116,34 +2116,34 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-5.128</v>
+        <v>-5.46</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-6.978</v>
+        <v>-7.79</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.393</v>
+        <v>-0.701</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-4.008</v>
+        <v>-5.084</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.626</v>
+        <v>-0.779</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.061</v>
+        <v>-2.692</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-7.423</v>
+        <v>-9.212999999999999</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-6.444</v>
+        <v>-8.739000000000001</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-8.327</v>
+        <v>-9.307</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-6.789</v>
+        <v>-7.896</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-3.377</v>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-2680.697996644125</v>
+        <v>-2760.279274927544</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-1622.515778296704</v>
+        <v>-1187.409401872652</v>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
@@ -2175,34 +2175,34 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-428.0467445742905</v>
+        <v>-455.7595993322204</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-118.9161554192229</v>
+        <v>-132.7539195637355</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>2.631755173106543</v>
+        <v>-4.694301212080627</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-25.1222264009026</v>
+        <v>-31.86661652250219</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>2.742606790799562</v>
+        <v>-3.412924424972618</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-2.476541711404697</v>
+        <v>-6.283553522244527</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-22.5739743940638</v>
+        <v>-28.0175166499407</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-24.33902402175555</v>
+        <v>-33.00725185073274</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-75.37110789283128</v>
+        <v>-84.24149167270095</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-59.74654580656517</v>
+        <v>-69.48869136671654</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>-41.27857230167461</v>
@@ -46042,7 +46042,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -48016,7 +48016,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -48968,7 +48968,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -51816,7 +51816,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -53254,7 +53254,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -53263,10 +53263,10 @@
         </is>
       </c>
       <c r="F484" s="5" t="n">
-        <v>-0.629922</v>
+        <v>0.629922</v>
       </c>
       <c r="G484" s="5" t="n">
-        <v>-1.147256</v>
+        <v>1.147256</v>
       </c>
       <c r="H484" t="inlineStr">
         <is>
